--- a/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（主界面、删除、复制、查询）-测试设计.xlsx
+++ b/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（主界面、删除、复制、查询）-测试设计.xlsx
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
   <si>
     <t>特性</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -305,10 +305,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>其他按钮测试（字符串模式、视图模式、展开、收起、最大化/最小化窗口弹出框、关闭弹出框按钮）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>复制记录时复制字段值并修改字段名后复制</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -509,14 +505,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>‘排序字段’字段名不存在</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>‘排序字段’值不存在</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1）值存在
 2）值不存在</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -560,6 +548,34 @@
   </si>
   <si>
     <t>其他按钮测试（最大化/最小化窗口弹出框、关闭弹出框按钮）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用‘排序方式’查询</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用‘扫描方式’查询</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘排序方式’字符串模式/展开/收起等按钮测试</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘扫描方式’字符串模式/展开/收起等按钮测试</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘匹配条件’字段名不存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘匹配条件’值不存在</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他按钮测试（字符串模式、视图模式、展开、收起、最大化/最小化窗口弹出框、关闭弹出框按钮）</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1058,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -1080,10 +1096,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -1134,7 +1150,7 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -1154,7 +1170,7 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -1186,7 +1202,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1329,7 +1345,7 @@
         <v>22</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1370,10 +1386,10 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F28" s="4"/>
     </row>
@@ -1382,10 +1398,10 @@
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F29" s="4"/>
     </row>
@@ -1404,7 +1420,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -1416,10 +1432,10 @@
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F32" s="4"/>
     </row>
@@ -1428,7 +1444,7 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -1458,7 +1474,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -1468,10 +1484,10 @@
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -1500,10 +1516,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F40" s="4"/>
     </row>
@@ -1512,10 +1528,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" s="4"/>
     </row>
@@ -1533,8 +1549,8 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="4" t="s">
-        <v>41</v>
+      <c r="D43" s="10" t="s">
+        <v>105</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -1544,7 +1560,7 @@
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -1554,11 +1570,11 @@
         <v>14</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -1568,7 +1584,7 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -1578,10 +1594,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F47" s="4"/>
     </row>
@@ -1590,10 +1606,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F48" s="4"/>
     </row>
@@ -1602,10 +1618,10 @@
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F49" s="4"/>
     </row>
@@ -1614,10 +1630,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F50" s="4"/>
     </row>
@@ -1626,7 +1642,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
@@ -1636,7 +1652,7 @@
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -1646,10 +1662,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F53" s="4"/>
     </row>
@@ -1658,7 +1674,7 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -1668,7 +1684,7 @@
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -1678,10 +1694,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F56" s="4"/>
     </row>
@@ -1690,10 +1706,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="F57" s="4"/>
     </row>
@@ -1702,10 +1718,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F58" s="4"/>
     </row>
@@ -1714,10 +1730,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F59" s="4"/>
     </row>
@@ -1726,10 +1742,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F60" s="4"/>
     </row>
@@ -1738,10 +1754,10 @@
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F61" s="4"/>
     </row>
@@ -1750,10 +1766,10 @@
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F62" s="4"/>
     </row>
@@ -1762,10 +1778,10 @@
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F63" s="4"/>
     </row>
@@ -1774,7 +1790,7 @@
       <c r="B64" s="1"/>
       <c r="C64" s="4"/>
       <c r="D64" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
@@ -1784,7 +1800,7 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -1794,7 +1810,7 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -1802,11 +1818,11 @@
     <row r="67" spans="1:6">
       <c r="A67" s="4"/>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -1816,7 +1832,7 @@
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
@@ -1826,7 +1842,7 @@
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
@@ -1836,7 +1852,7 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
@@ -1846,7 +1862,7 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
@@ -1855,7 +1871,9 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
+      <c r="D72" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
     </row>
@@ -1863,7 +1881,9 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
+      <c r="D73" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
     </row>
@@ -1871,7 +1891,9 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
+      <c r="D74" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
     </row>
@@ -1879,7 +1901,9 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
+      <c r="D75" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
     </row>
@@ -1926,7 +1950,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
-      <c r="C81" s="6"/>
+      <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
@@ -1942,7 +1966,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
+      <c r="C83" s="6"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
@@ -2075,6 +2099,22 @@
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
     </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
